--- a/clino_scattering_planes.xlsx
+++ b/clino_scattering_planes.xlsx
@@ -510,7 +510,7 @@
       <c r="I2" t="n">
         <v>15.24705525690479</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -539,12 +539,12 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-163.6345873441618</v>
+        <v>196.3654126558382</v>
       </c>
       <c r="I3" t="n">
         <v>15.24701048178853</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -573,13 +573,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>376.3654696312377</v>
+        <v>16.36546963123766</v>
       </c>
       <c r="I4" t="n">
         <v>15.24693060735993</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
+      <c r="J4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -612,7 +612,7 @@
       <c r="I5" t="n">
         <v>15.24571639765113</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -641,12 +641,12 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>-73.63467830802186</v>
+        <v>286.3653216919781</v>
       </c>
       <c r="I6" t="n">
         <v>14.94598937456372</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -680,7 +680,7 @@
       <c r="I7" t="n">
         <v>14.94590077062923</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -714,7 +714,7 @@
       <c r="I8" t="n">
         <v>14.94576814017513</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -743,12 +743,12 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>-73.6347226243662</v>
+        <v>286.3652773756338</v>
       </c>
       <c r="I9" t="n">
         <v>14.94581610481091</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -777,12 +777,12 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>-80.75929433524158</v>
+        <v>279.2407056647584</v>
       </c>
       <c r="I10" t="n">
         <v>107.6843191406174</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -811,12 +811,12 @@
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>459.2406869024605</v>
+        <v>99.24068690246048</v>
       </c>
       <c r="I11" t="n">
-        <v>-252.315883588018</v>
-      </c>
-      <c r="J11" t="n">
+        <v>107.684116411982</v>
+      </c>
+      <c r="J11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -845,12 +845,12 @@
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>-99.24076200953557</v>
+        <v>260.7592379904644</v>
       </c>
       <c r="I12" t="n">
-        <v>-432.3156296736273</v>
-      </c>
-      <c r="J12" t="n">
+        <v>287.6843703263727</v>
+      </c>
+      <c r="J12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -879,12 +879,12 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>-99.24068903453555</v>
+        <v>260.7593109654645</v>
       </c>
       <c r="I13" t="n">
-        <v>-72.31589085216753</v>
-      </c>
-      <c r="J13" t="n">
+        <v>287.6841091478325</v>
+      </c>
+      <c r="J13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -913,12 +913,12 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>-84.17327527939591</v>
+        <v>275.8267247206041</v>
       </c>
       <c r="I14" t="n">
-        <v>-26.66870275754673</v>
-      </c>
-      <c r="J14" t="n">
+        <v>333.3312972424533</v>
+      </c>
+      <c r="J14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -947,12 +947,12 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>-84.17331914366599</v>
+        <v>275.826680856334</v>
       </c>
       <c r="I15" t="n">
-        <v>-26.66885699994053</v>
-      </c>
-      <c r="J15" t="n">
+        <v>333.3311430000595</v>
+      </c>
+      <c r="J15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -984,9 +984,9 @@
         <v>95.82634433098487</v>
       </c>
       <c r="I16" t="n">
-        <v>-26.66890115199736</v>
-      </c>
-      <c r="J16" t="n">
+        <v>333.3310988480026</v>
+      </c>
+      <c r="J16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1018,9 +1018,9 @@
         <v>95.82686803262371</v>
       </c>
       <c r="I17" t="n">
-        <v>-26.66885017846564</v>
-      </c>
-      <c r="J17" t="n">
+        <v>333.3311498215344</v>
+      </c>
+      <c r="J17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-34.4931474593764</v>
+        <v>325.5068525406236</v>
       </c>
       <c r="I18" t="n">
         <v>130.2470757726207</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1086,10 +1086,10 @@
         <v>34.49334922742212</v>
       </c>
       <c r="I19" t="n">
-        <v>-49.75226630834369</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
+        <v>310.2477336916563</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1117,12 +1117,12 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-214.493324265184</v>
+        <v>145.506675734816</v>
       </c>
       <c r="I20" t="n">
         <v>130.2473581093853</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1154,10 +1154,10 @@
         <v>34.49321932543143</v>
       </c>
       <c r="I21" t="n">
-        <v>-49.75291064269307</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
+        <v>310.2470893573069</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1190,7 +1190,7 @@
       <c r="I22" t="n">
         <v>14.75155044961241</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       <c r="I23" t="n">
         <v>14.75057443453965</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="I24" t="n">
         <v>14.75150994079709</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1290,10 +1290,10 @@
         <v>20.38793714860336</v>
       </c>
       <c r="I25" t="n">
-        <v>-165.2488908882795</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
+        <v>194.7511091117205</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1321,12 +1321,12 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>-468.4659932810428</v>
+        <v>251.5340067189572</v>
       </c>
       <c r="I26" t="n">
-        <v>-480.9032102894095</v>
-      </c>
-      <c r="J26" t="n">
+        <v>239.0967897105905</v>
+      </c>
+      <c r="J26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>-251.5336829280617</v>
+        <v>108.4663170719383</v>
       </c>
       <c r="I27" t="n">
         <v>59.09673816337565</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       <c r="I28" t="n">
         <v>59.09687404470438</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       <c r="I29" t="n">
         <v>59.09699590329742</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="I30" t="n">
         <v>84.38029043267113</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-39.89497451931658</v>
+        <v>320.1050254806834</v>
       </c>
       <c r="I31" t="n">
-        <v>-95.61901505911408</v>
-      </c>
-      <c r="J31" t="n">
+        <v>264.3809849408859</v>
+      </c>
+      <c r="J31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       <c r="I32" t="n">
         <v>84.38027527697608</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-39.89496622419782</v>
+        <v>320.1050337758022</v>
       </c>
       <c r="I33" t="n">
-        <v>-95.61898081715771</v>
-      </c>
-      <c r="J33" t="n">
+        <v>264.3810191828423</v>
+      </c>
+      <c r="J33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       <c r="I34" t="n">
         <v>15.03092225791461</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       <c r="I35" t="n">
         <v>15.03048069096935</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>-126.8816489351713</v>
+        <v>233.1183510648287</v>
       </c>
       <c r="I36" t="n">
         <v>15.03096397597807</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>-486.8817630874536</v>
+        <v>233.1182369125464</v>
       </c>
       <c r="I37" t="n">
-        <v>375.0307310259893</v>
-      </c>
-      <c r="J37" t="n">
+        <v>15.03073102598933</v>
+      </c>
+      <c r="J37" t="b">
         <v>0</v>
       </c>
     </row>
